--- a/CalculatorAutomation/src/test/resources/TestData.xlsx
+++ b/CalculatorAutomation/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestNG_Programs\CalculatorAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8637BD13-77EB-4004-9357-84DC417E2C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B265F199-7D2E-4161-A07B-723C90F4C854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{617CC904-D425-48D7-9844-B61ACCA85D9B}"/>
   </bookViews>
@@ -36,16 +36,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Player</t>
+    <t>State</t>
   </si>
   <si>
-    <t>Team</t>
+    <t>Capital</t>
   </si>
   <si>
-    <t>Dhoni</t>
+    <t>Tamilnadu</t>
   </si>
   <si>
-    <t>CSK</t>
+    <t>Chennai</t>
   </si>
 </sst>
 </file>
@@ -399,6 +399,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95F96B2-11EC-4B51-AAEF-33D7F8C50B44}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
